--- a/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -415,140 +415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:
-战场
-11 猎魔
-12 曙光</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">怪物类型
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
-          </rPr>
-          <t>0</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">：通用
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">：野兽
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">：人物
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>：恶魔</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC3" authorId="1">
+    <comment ref="Z3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -562,7 +429,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE3" authorId="1">
+    <comment ref="AB3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -596,7 +463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF3" authorId="1">
+    <comment ref="AC3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -647,7 +514,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI3" authorId="1">
+    <comment ref="AF3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -663,7 +530,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK3" authorId="0">
+    <comment ref="AH3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -689,27 +556,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="AL3" authorId="0">
+    <comment ref="AI3" authorId="1">
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
             <charset val="134"/>
           </rPr>
-          <t>Administrator:</t>
+          <t>作者:
+怪物掉落道具的掉落表ID</t>
         </r>
+      </text>
+    </comment>
+    <comment ref="AL3" authorId="1">
+      <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="Helvetica Neue"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">
-0：看见就有掉落
-1：造成伤害才有掉落
-</t>
+          <t>作者:
+怪物技能ID</t>
         </r>
       </text>
     </comment>
@@ -723,62 +594,11 @@
             <charset val="134"/>
           </rPr>
           <t>作者:
-怪物掉落道具的掉落表ID</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AN3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:
-最小等级;最大等级;掉落ID1,掉落ID2</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AQ3" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:
 怪物技能ID</t>
         </r>
       </text>
     </comment>
-    <comment ref="AR3" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:
-怪物技能ID</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AS3" authorId="2">
+    <comment ref="AN3" authorId="2">
       <text>
         <r>
           <rPr>
@@ -801,7 +621,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AT3" authorId="0">
+    <comment ref="AO3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -825,7 +645,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AU3" authorId="1">
+    <comment ref="AP3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -839,7 +659,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AW3" authorId="1">
+    <comment ref="AR3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -853,7 +673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AZ3" authorId="0">
+    <comment ref="AT3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -877,54 +697,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-对敌人隐身,如果对敌人攻击或使用主动技能就会现身
-0 默认 不隐身
-1 隐身</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BB3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-0 带走
-1 不带走</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BC3" authorId="0">
+    <comment ref="AU3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -971,37 +744,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="BD3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-支持A，B
-A 宝宝抓捕激活
-B 变异抓捕激活
-如果只配一个，默认变异也激活第一个</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="96">
   <si>
     <t>c</t>
   </si>
@@ -1018,24 +766,15 @@
     <t>怪物子类</t>
   </si>
   <si>
-    <t>阵营</t>
-  </si>
-  <si>
-    <t>怪物种族</t>
-  </si>
-  <si>
     <t>怪物头像</t>
   </si>
   <si>
+    <t>怪物阵营</t>
+  </si>
+  <si>
     <t>怪物模型ID</t>
   </si>
   <si>
-    <t>触发精灵概率</t>
-  </si>
-  <si>
-    <t>触发精灵ID</t>
-  </si>
-  <si>
     <t>怪物等级</t>
   </si>
   <si>
@@ -1111,15 +850,9 @@
     <t>掉落类型</t>
   </si>
   <si>
-    <t>造成伤害才有掉落</t>
-  </si>
-  <si>
     <t>掉落ID</t>
   </si>
   <si>
-    <t>分级掉落</t>
-  </si>
-  <si>
     <t>极品掉落概率</t>
   </si>
   <si>
@@ -1150,24 +883,12 @@
     <t>怪物死亡触发技能</t>
   </si>
   <si>
-    <t>开服天数刷怪变化</t>
-  </si>
-  <si>
     <t>攻击初始位置</t>
   </si>
   <si>
-    <t>是否对敌人隐身</t>
-  </si>
-  <si>
-    <t>是否带走buff</t>
-  </si>
-  <si>
     <t>怪物显示的位置</t>
   </si>
   <si>
-    <t>奇遇宠物id</t>
-  </si>
-  <si>
     <t>MonsterName</t>
   </si>
   <si>
@@ -1177,24 +898,15 @@
     <t>MonsterSonType</t>
   </si>
   <si>
+    <t>MonsterHeadIcon</t>
+  </si>
+  <si>
     <t>MonsterCamp</t>
   </si>
   <si>
-    <t>MonsterRace</t>
-  </si>
-  <si>
-    <t>MonsterHeadIcon</t>
-  </si>
-  <si>
     <t>MonsterModelID</t>
   </si>
   <si>
-    <t>SpiritPro</t>
-  </si>
-  <si>
-    <t>SpiritID</t>
-  </si>
-  <si>
     <t>Lv</t>
   </si>
   <si>
@@ -1270,15 +982,9 @@
     <t>DropType</t>
   </si>
   <si>
-    <t>IfDamgeDrop</t>
-  </si>
-  <si>
     <t>DropID</t>
   </si>
   <si>
-    <t>LvDropID</t>
-  </si>
-  <si>
     <t>HideDropPro</t>
   </si>
   <si>
@@ -1306,22 +1012,10 @@
     <t>DeathSkillId</t>
   </si>
   <si>
-    <t>OpenDayMonster</t>
-  </si>
-  <si>
     <t>ActBasePosiY</t>
   </si>
   <si>
-    <t>IfHide</t>
-  </si>
-  <si>
-    <t>RemoveBuff</t>
-  </si>
-  <si>
     <t>ModelShowPosi</t>
-  </si>
-  <si>
-    <t>QiYuPetId</t>
   </si>
   <si>
     <t>int</t>
@@ -1355,7 +1049,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1380,13 +1074,6 @@
       <color indexed="9"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1564,14 +1251,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1592,13 +1284,8 @@
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="43">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1614,12 +1301,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="10"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1852,7 +1533,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1884,19 +1565,6 @@
       </right>
       <top style="thin">
         <color indexed="9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -2030,67 +1698,70 @@
   </borders>
   <cellStyleXfs count="888">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2105,2502 +1776,2499 @@
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4620,16 +4288,13 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="627" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5546,7 +5211,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{13715800-E622-4ACF-A666-8DF257909111}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{915D4505-2DEC-4B2A-95BB-A2B169F6115C}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -6698,60 +6363,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:BD6"/>
+  <dimension ref="C1:AU6"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1" outlineLevelRow="5"/>
   <cols>
     <col min="3" max="3" width="8.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="29.625" style="2" customWidth="1"/>
     <col min="5" max="5" width="13.875" style="2" customWidth="1"/>
-    <col min="6" max="7" width="14.25" style="2" customWidth="1"/>
-    <col min="8" max="10" width="15" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.875" style="2" customWidth="1"/>
-    <col min="14" max="15" width="19" style="2" customWidth="1"/>
-    <col min="16" max="17" width="14.5" style="2" customWidth="1"/>
-    <col min="18" max="18" width="15.5" style="2" customWidth="1"/>
-    <col min="19" max="19" width="20.125" style="2" customWidth="1"/>
-    <col min="20" max="20" width="21.375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="16" style="2" customWidth="1"/>
-    <col min="22" max="22" width="16.625" style="2" customWidth="1"/>
-    <col min="23" max="23" width="16" style="2" customWidth="1"/>
-    <col min="24" max="27" width="11.375" style="2" customWidth="1"/>
-    <col min="28" max="28" width="8.5" style="2" customWidth="1"/>
-    <col min="29" max="29" width="11.375" style="2" customWidth="1"/>
-    <col min="30" max="30" width="11.25" style="2" customWidth="1"/>
-    <col min="31" max="31" width="10.25" style="2" customWidth="1"/>
-    <col min="32" max="32" width="11.25" style="2" customWidth="1"/>
-    <col min="33" max="33" width="15.125" style="2" customWidth="1"/>
-    <col min="34" max="34" width="12.25" style="2" customWidth="1"/>
-    <col min="35" max="35" width="14.375" style="2" customWidth="1"/>
-    <col min="36" max="37" width="10.25" style="2" customWidth="1"/>
-    <col min="38" max="38" width="14" style="2" customWidth="1"/>
-    <col min="39" max="39" width="188.875" style="3" customWidth="1"/>
-    <col min="40" max="40" width="59.125" style="2" customWidth="1"/>
-    <col min="41" max="41" width="11.375" style="2" customWidth="1"/>
-    <col min="42" max="43" width="14.125" style="2" customWidth="1"/>
-    <col min="44" max="44" width="95.75" style="2" customWidth="1"/>
-    <col min="45" max="45" width="35.125" style="2" customWidth="1"/>
-    <col min="46" max="46" width="17.125" style="2" customWidth="1"/>
-    <col min="47" max="48" width="32.75" style="2" customWidth="1"/>
-    <col min="49" max="49" width="16.875" style="2" customWidth="1"/>
-    <col min="50" max="50" width="25.875" style="2" customWidth="1"/>
-    <col min="51" max="51" width="34.625" customWidth="1"/>
-    <col min="52" max="52" width="14.125" style="2" customWidth="1"/>
-    <col min="53" max="56" width="25.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="2" customWidth="1"/>
+    <col min="7" max="9" width="15" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.875" style="2" customWidth="1"/>
+    <col min="11" max="12" width="19" style="2" customWidth="1"/>
+    <col min="13" max="14" width="14.5" style="2" customWidth="1"/>
+    <col min="15" max="15" width="15.5" style="2" customWidth="1"/>
+    <col min="16" max="16" width="20.125" style="2" customWidth="1"/>
+    <col min="17" max="17" width="21.375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="16" style="2" customWidth="1"/>
+    <col min="19" max="19" width="16.625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="16" style="2" customWidth="1"/>
+    <col min="21" max="24" width="11.375" style="2" customWidth="1"/>
+    <col min="25" max="25" width="8.5" style="2" customWidth="1"/>
+    <col min="26" max="26" width="11.375" style="2" customWidth="1"/>
+    <col min="27" max="27" width="11.25" style="2" customWidth="1"/>
+    <col min="28" max="28" width="10.25" style="2" customWidth="1"/>
+    <col min="29" max="29" width="11.25" style="2" customWidth="1"/>
+    <col min="30" max="30" width="15.125" style="2" customWidth="1"/>
+    <col min="31" max="31" width="12.25" style="2" customWidth="1"/>
+    <col min="32" max="32" width="14.375" style="2" customWidth="1"/>
+    <col min="33" max="34" width="10.25" style="2" customWidth="1"/>
+    <col min="35" max="35" width="73.625" style="3" customWidth="1"/>
+    <col min="36" max="36" width="11.375" style="2" customWidth="1"/>
+    <col min="37" max="38" width="14.125" style="2" customWidth="1"/>
+    <col min="39" max="39" width="12.875" style="2" customWidth="1"/>
+    <col min="40" max="40" width="25.375" style="2" customWidth="1"/>
+    <col min="41" max="41" width="17.125" style="2" customWidth="1"/>
+    <col min="42" max="43" width="32.75" style="2" customWidth="1"/>
+    <col min="44" max="44" width="16.875" style="2" customWidth="1"/>
+    <col min="45" max="45" width="25.875" style="2" customWidth="1"/>
+    <col min="46" max="46" width="14.125" style="2" customWidth="1"/>
+    <col min="47" max="47" width="25.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="3:56">
-      <c r="AM1" s="4"/>
+    <row r="1" s="1" customFormat="1" ht="14.25" spans="3:47">
+      <c r="AI1" s="4"/>
     </row>
-    <row r="2" customHeight="1" spans="3:56">
-      <c r="BC2" s="2" t="s">
+    <row r="2" customHeight="1" spans="3:47">
+      <c r="AU2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:56">
+    <row r="3" ht="20.1" customHeight="1" spans="3:47">
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
@@ -6887,510 +6547,406 @@
       <c r="AU3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AV3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="AW3" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AX3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AY3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AZ3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="BA3" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="BB3" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="BC3" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="BD3" s="6" t="s">
-        <v>54</v>
-      </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:56">
+    <row r="4" ht="20.1" customHeight="1" spans="3:47">
       <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M4" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="N4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="O4" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="P4" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="Q4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="R4" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="S4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="T4" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="U4" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="V4" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="W4" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="X4" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="Y4" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="Z4" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="AA4" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="AB4" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="AC4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="U4" s="7" t="s">
+      <c r="AD4" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="V4" s="7" t="s">
+      <c r="AE4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="W4" s="7" t="s">
+      <c r="AF4" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="X4" s="7" t="s">
+      <c r="AG4" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="Y4" s="7" t="s">
+      <c r="AH4" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="Z4" s="7" t="s">
+      <c r="AI4" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="AA4" s="7" t="s">
+      <c r="AJ4" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="AB4" s="7" t="s">
+      <c r="AK4" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="AC4" s="7" t="s">
+      <c r="AL4" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AD4" s="7" t="s">
+      <c r="AM4" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="AE4" s="7" t="s">
+      <c r="AN4" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="AF4" s="7" t="s">
+      <c r="AO4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP4" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="AG4" s="7" t="s">
+      <c r="AQ4" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="AH4" s="7" t="s">
+      <c r="AR4" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="AI4" s="7" t="s">
+      <c r="AS4" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="AJ4" s="7" t="s">
+      <c r="AT4" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="AK4" s="7" t="s">
+      <c r="AU4" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="AL4" s="7" t="s">
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="3:47">
+      <c r="C5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AM4" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="AN4" s="7" t="s">
+      <c r="E5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="AO4" s="7" t="s">
+      <c r="L5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI5" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="AP4" s="7" t="s">
+      <c r="AJ5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AK5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM5" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN5" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AP5" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AU5" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="3:47">
+      <c r="C6" s="10">
+        <v>310101</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="AQ4" s="7" t="s">
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10">
+        <v>310105</v>
+      </c>
+      <c r="H6" s="10">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10">
+        <v>330101</v>
+      </c>
+      <c r="J6" s="10">
+        <v>9</v>
+      </c>
+      <c r="K6" s="10">
+        <v>3</v>
+      </c>
+      <c r="L6" s="10">
+        <v>2</v>
+      </c>
+      <c r="M6" s="10">
+        <v>1</v>
+      </c>
+      <c r="N6" s="10">
+        <v>5250</v>
+      </c>
+      <c r="O6" s="10">
+        <v>500</v>
+      </c>
+      <c r="P6" s="10">
+        <v>500</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>150</v>
+      </c>
+      <c r="R6" s="10">
+        <v>150</v>
+      </c>
+      <c r="S6" s="10">
+        <v>0</v>
+      </c>
+      <c r="T6" s="10">
+        <v>0</v>
+      </c>
+      <c r="U6" s="10">
+        <v>0</v>
+      </c>
+      <c r="V6" s="10">
+        <v>0</v>
+      </c>
+      <c r="W6" s="10">
+        <v>0</v>
+      </c>
+      <c r="X6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="10">
+        <v>60</v>
+      </c>
+      <c r="AA6" s="10">
+        <v>3</v>
+      </c>
+      <c r="AB6" s="10">
+        <v>30</v>
+      </c>
+      <c r="AC6" s="10">
+        <v>4</v>
+      </c>
+      <c r="AD6" s="10">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="10">
+        <v>80</v>
+      </c>
+      <c r="AF6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="10">
+        <v>2</v>
+      </c>
+      <c r="AI6" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="AR4" s="7" t="s">
+      <c r="AJ6" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="AK6" s="10">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="10">
+        <v>2001013</v>
+      </c>
+      <c r="AM6" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="AS4" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AT4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU4" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AV4" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="AW4" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="AX4" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="AY4" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="AZ4" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="BA4" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="BB4" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="BC4" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="BD4" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:56">
-      <c r="C5" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="V5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="W5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="X5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="AC5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="AD5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="AE5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="AF5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="AG5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="AH5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="AJ5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="AK5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="AL5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="AM5" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AN5" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AO5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="AQ5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="AR5" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AS5" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AT5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="AU5" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AV5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="AW5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="AX5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="AY5" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AZ5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="BA5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="BB5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="BC5" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="BD5" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" ht="20.1" customHeight="1" spans="3:56">
-      <c r="C6" s="11">
-        <v>310101</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" s="11">
+      <c r="AN6" s="10"/>
+      <c r="AO6" s="10">
         <v>1</v>
       </c>
-      <c r="F6" s="11">
+      <c r="AP6" s="10"/>
+      <c r="AQ6" s="10"/>
+      <c r="AR6" s="10"/>
+      <c r="AS6" s="10"/>
+      <c r="AT6" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AU6" s="10">
         <v>0</v>
-      </c>
-      <c r="G6" s="11">
-        <v>0</v>
-      </c>
-      <c r="H6" s="11">
-        <v>0</v>
-      </c>
-      <c r="I6" s="11">
-        <v>310105</v>
-      </c>
-      <c r="J6" s="11">
-        <v>330101</v>
-      </c>
-      <c r="K6" s="11">
-        <v>0</v>
-      </c>
-      <c r="L6" s="11">
-        <v>0</v>
-      </c>
-      <c r="M6" s="11">
-        <v>9</v>
-      </c>
-      <c r="N6" s="11">
-        <v>3</v>
-      </c>
-      <c r="O6" s="11">
-        <v>2</v>
-      </c>
-      <c r="P6" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>5250</v>
-      </c>
-      <c r="R6" s="11">
-        <v>500</v>
-      </c>
-      <c r="S6" s="11">
-        <v>500</v>
-      </c>
-      <c r="T6" s="11">
-        <v>150</v>
-      </c>
-      <c r="U6" s="11">
-        <v>150</v>
-      </c>
-      <c r="V6" s="11">
-        <v>0</v>
-      </c>
-      <c r="W6" s="11">
-        <v>0</v>
-      </c>
-      <c r="X6" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="11">
-        <v>60</v>
-      </c>
-      <c r="AD6" s="11">
-        <v>3</v>
-      </c>
-      <c r="AE6" s="11">
-        <v>30</v>
-      </c>
-      <c r="AF6" s="11">
-        <v>4</v>
-      </c>
-      <c r="AG6" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="11">
-        <v>80</v>
-      </c>
-      <c r="AI6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="11">
-        <v>1</v>
-      </c>
-      <c r="AK6" s="11">
-        <v>2</v>
-      </c>
-      <c r="AL6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="AN6" s="12"/>
-      <c r="AO6" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="AP6" s="11">
-        <v>1</v>
-      </c>
-      <c r="AQ6" s="11">
-        <v>2001013</v>
-      </c>
-      <c r="AR6" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="AS6" s="11"/>
-      <c r="AT6" s="11">
-        <v>1</v>
-      </c>
-      <c r="AU6" s="11"/>
-      <c r="AV6" s="11"/>
-      <c r="AW6" s="11"/>
-      <c r="AX6" s="11"/>
-      <c r="AY6" s="11"/>
-      <c r="AZ6" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="BA6" s="11">
-        <v>0</v>
-      </c>
-      <c r="BB6" s="11">
-        <v>0</v>
-      </c>
-      <c r="BC6" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD6" s="11">
-        <v>310105</v>
       </c>
     </row>
   </sheetData>
